--- a/data/trans_orig/P16A07-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16A07-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antidepresivos en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido antidepresivos en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14536</t>
+          <t>13808</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33552</t>
+          <t>32141</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31620</t>
+          <t>30139</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55216</t>
+          <t>56316</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49927</t>
+          <t>49926</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>78707</t>
+          <t>79264</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>659442</t>
+          <t>660853</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>678458</t>
+          <t>679186</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>633135</t>
+          <t>632035</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>656731</t>
+          <t>658212</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1302638</t>
+          <t>1302081</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1331418</t>
+          <t>1331419</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14025</t>
+          <t>14541</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35112</t>
+          <t>33164</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49714</t>
+          <t>48923</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80015</t>
+          <t>81258</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>68562</t>
+          <t>68845</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>106320</t>
+          <t>104956</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>926688</t>
+          <t>928636</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>947775</t>
+          <t>947259</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>888378</t>
+          <t>887135</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>918679</t>
+          <t>919470</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1823873</t>
+          <t>1825237</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1861631</t>
+          <t>1861348</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>4872</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17357</t>
+          <t>16854</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27205</t>
+          <t>28956</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52687</t>
+          <t>52154</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37290</t>
+          <t>36611</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63654</t>
+          <t>63616</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>661152</t>
+          <t>661655</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>673546</t>
+          <t>673637</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>631154</t>
+          <t>631687</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>656636</t>
+          <t>654885</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1298696</t>
+          <t>1298734</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1325060</t>
+          <t>1325739</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,31%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10260</t>
+          <t>10139</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26057</t>
+          <t>25731</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59187</t>
+          <t>58367</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>93091</t>
+          <t>92572</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>73958</t>
+          <t>72946</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>110903</t>
+          <t>110724</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>916165</t>
+          <t>916491</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>931962</t>
+          <t>932083</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>945521</t>
+          <t>946040</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>979425</t>
+          <t>980245</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1869931</t>
+          <t>1870110</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1906876</t>
+          <t>1907888</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,32%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>55089</t>
+          <t>55132</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>85755</t>
+          <t>88484</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>190280</t>
+          <t>190996</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>246748</t>
+          <t>247695</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>255230</t>
+          <t>259067</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>320257</t>
+          <t>319516</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3189770</t>
+          <t>3187041</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3220436</t>
+          <t>3220393</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3132449</t>
+          <t>3131502</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3188917</t>
+          <t>3188201</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6334465</t>
+          <t>6335206</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6399492</t>
+          <t>6395655</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,11%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antidepresivos en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido antidepresivos en las dos últimas semanas en 2012 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10881</t>
+          <t>10729</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27848</t>
+          <t>29094</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>52988</t>
+          <t>53560</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>84340</t>
+          <t>84617</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>68797</t>
+          <t>70995</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>105588</t>
+          <t>107857</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>672916</t>
+          <t>671670</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>689883</t>
+          <t>690035</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>610733</t>
+          <t>610456</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>642085</t>
+          <t>641513</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1290249</t>
+          <t>1287980</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1327040</t>
+          <t>1324842</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,91%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25494</t>
+          <t>24320</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51440</t>
+          <t>50697</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65639</t>
+          <t>67217</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>103526</t>
+          <t>102157</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>100058</t>
+          <t>99013</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>143702</t>
+          <t>142863</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>966507</t>
+          <t>967250</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>992453</t>
+          <t>993627</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>923169</t>
+          <t>924538</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>961056</t>
+          <t>959478</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1900940</t>
+          <t>1901779</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1944584</t>
+          <t>1945629</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,16%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8274</t>
+          <t>8247</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29332</t>
+          <t>28074</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40403</t>
+          <t>40979</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70774</t>
+          <t>72308</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55107</t>
+          <t>55592</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>90978</t>
+          <t>91426</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>726165</t>
+          <t>727423</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>747223</t>
+          <t>747250</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>705509</t>
+          <t>703975</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>735880</t>
+          <t>735304</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1440802</t>
+          <t>1440354</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1476673</t>
+          <t>1476188</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,37%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26057</t>
+          <t>24926</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54281</t>
+          <t>52906</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71998</t>
+          <t>72192</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>108100</t>
+          <t>108782</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>105854</t>
+          <t>104745</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>150864</t>
+          <t>150736</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>889658</t>
+          <t>891033</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>917882</t>
+          <t>919013</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>940663</t>
+          <t>939981</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>976765</t>
+          <t>976571</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1841839</t>
+          <t>1841967</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1886849</t>
+          <t>1887958</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,74%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>86572</t>
+          <t>86537</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>133555</t>
+          <t>132995</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>262752</t>
+          <t>264554</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>328478</t>
+          <t>331394</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>367529</t>
+          <t>364473</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>448340</t>
+          <t>448511</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3284592</t>
+          <t>3285152</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3331575</t>
+          <t>3331610</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3218337</t>
+          <t>3215421</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3284063</t>
+          <t>3282261</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6516621</t>
+          <t>6516450</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6597432</t>
+          <t>6600488</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,77%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antidepresivos en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido antidepresivos en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6529</t>
+          <t>6879</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20711</t>
+          <t>21308</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>43872</t>
+          <t>45034</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>72340</t>
+          <t>73523</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54761</t>
+          <t>55104</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>88079</t>
+          <t>86750</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>654089</t>
+          <t>653492</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>668271</t>
+          <t>667921</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>600499</t>
+          <t>599316</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>628967</t>
+          <t>627805</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1259560</t>
+          <t>1260889</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1292878</t>
+          <t>1292535</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,91%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10234</t>
+          <t>10464</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27066</t>
+          <t>26873</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60575</t>
+          <t>60712</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>94242</t>
+          <t>94435</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>76501</t>
+          <t>76703</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>114119</t>
+          <t>114567</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>995365</t>
+          <t>995558</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1012197</t>
+          <t>1011967</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>948671</t>
+          <t>948478</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>982338</t>
+          <t>982201</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1951225</t>
+          <t>1950777</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1988843</t>
+          <t>1988641</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,29%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9265</t>
+          <t>8834</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26416</t>
+          <t>25533</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30834</t>
+          <t>31150</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57412</t>
+          <t>58152</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43634</t>
+          <t>43784</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>75595</t>
+          <t>76220</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>733136</t>
+          <t>734019</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>750287</t>
+          <t>750718</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>727599</t>
+          <t>726859</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>754177</t>
+          <t>753861</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1468968</t>
+          <t>1468343</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1500929</t>
+          <t>1500779</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,17%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19593</t>
+          <t>19398</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40806</t>
+          <t>40854</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59443</t>
+          <t>59250</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>94412</t>
+          <t>95609</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>83928</t>
+          <t>85580</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>125948</t>
+          <t>124274</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>896761</t>
+          <t>896713</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>917974</t>
+          <t>918169</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>949367</t>
+          <t>948170</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>984336</t>
+          <t>984529</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1855398</t>
+          <t>1857072</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1897418</t>
+          <t>1895766</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,68%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>57849</t>
+          <t>58629</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>91412</t>
+          <t>92928</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>223043</t>
+          <t>220920</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>283410</t>
+          <t>288598</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>290464</t>
+          <t>294186</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>362774</t>
+          <t>365908</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3302938</t>
+          <t>3301422</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3336501</t>
+          <t>3335721</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3261132</t>
+          <t>3255944</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3321499</t>
+          <t>3323622</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6576118</t>
+          <t>6572984</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6648428</t>
+          <t>6644706</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,76%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antidepresivos en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido antidepresivos en las dos últimas semanas en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21663</t>
+          <t>22055</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42884</t>
+          <t>43288</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37525</t>
+          <t>36975</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55772</t>
+          <t>56402</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>63473</t>
+          <t>62327</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>91388</t>
+          <t>90678</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>592067</t>
+          <t>591663</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>613288</t>
+          <t>612896</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>619650</t>
+          <t>619020</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>637897</t>
+          <t>638447</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1218985</t>
+          <t>1219695</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1246900</t>
+          <t>1248046</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,24%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12566</t>
+          <t>12015</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38192</t>
+          <t>37703</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51646</t>
+          <t>52380</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73896</t>
+          <t>76182</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>54579</t>
+          <t>57894</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>105795</t>
+          <t>106141</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1154672</t>
+          <t>1155161</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1180298</t>
+          <t>1180849</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>884210</t>
+          <t>881924</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>906460</t>
+          <t>905726</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2045176</t>
+          <t>2044830</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2096392</t>
+          <t>2093077</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,31%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14708</t>
+          <t>15521</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33934</t>
+          <t>35068</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30140</t>
+          <t>31075</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>84294</t>
+          <t>85083</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56754</t>
+          <t>54283</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>105750</t>
+          <t>105554</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>669750</t>
+          <t>668616</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>688976</t>
+          <t>688163</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>848506</t>
+          <t>847717</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>902660</t>
+          <t>901725</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1530734</t>
+          <t>1530930</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1579730</t>
+          <t>1582201</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,68%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23461</t>
+          <t>24047</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44176</t>
+          <t>44002</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>73527</t>
+          <t>72509</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>110669</t>
+          <t>109459</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>107701</t>
+          <t>106090</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>146366</t>
+          <t>147207</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,29%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>882655</t>
+          <t>882829</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>903370</t>
+          <t>902784</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>980705</t>
+          <t>981915</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1017847</t>
+          <t>1018865</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1871839</t>
+          <t>1870998</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1910504</t>
+          <t>1912115</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,74%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>84745</t>
+          <t>85505</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>135474</t>
+          <t>134337</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>210501</t>
+          <t>214142</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>291456</t>
+          <t>293572</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>322144</t>
+          <t>323773</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>414280</t>
+          <t>413007</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3322856</t>
+          <t>3323993</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3373585</t>
+          <t>3372825</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3366246</t>
+          <t>3364130</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3447201</t>
+          <t>3443560</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6701752</t>
+          <t>6703025</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6793888</t>
+          <t>6792259</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,45%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A07-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16A07-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13808</t>
+          <t>13481</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32141</t>
+          <t>31029</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30139</t>
+          <t>29282</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56316</t>
+          <t>53243</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49926</t>
+          <t>48534</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79264</t>
+          <t>78336</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>660853</t>
+          <t>661965</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>679186</t>
+          <t>679513</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>632035</t>
+          <t>635108</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>658212</t>
+          <t>659069</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1302081</t>
+          <t>1303009</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1331419</t>
+          <t>1332811</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,49%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14541</t>
+          <t>13948</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33164</t>
+          <t>32829</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>48923</t>
+          <t>48493</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>81258</t>
+          <t>79855</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>68845</t>
+          <t>68239</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>104956</t>
+          <t>104573</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>928636</t>
+          <t>928971</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>947259</t>
+          <t>947852</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>887135</t>
+          <t>888538</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>919470</t>
+          <t>919900</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1825237</t>
+          <t>1825620</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1861348</t>
+          <t>1861954</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4872</t>
+          <t>4798</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16854</t>
+          <t>17446</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28956</t>
+          <t>28341</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52154</t>
+          <t>51624</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36611</t>
+          <t>36673</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63616</t>
+          <t>64126</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>661655</t>
+          <t>661063</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>673637</t>
+          <t>673711</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>631687</t>
+          <t>632217</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>654885</t>
+          <t>655500</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1298734</t>
+          <t>1298224</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1325739</t>
+          <t>1325677</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10139</t>
+          <t>10181</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25731</t>
+          <t>27039</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58367</t>
+          <t>57790</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>92572</t>
+          <t>90864</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>72946</t>
+          <t>74100</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>110724</t>
+          <t>114153</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>916491</t>
+          <t>915183</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>932083</t>
+          <t>932041</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>946040</t>
+          <t>947748</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>980245</t>
+          <t>980822</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1870110</t>
+          <t>1866681</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1907888</t>
+          <t>1906734</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,26%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>55132</t>
+          <t>54910</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>88484</t>
+          <t>87621</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>190996</t>
+          <t>190667</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>247695</t>
+          <t>247809</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>259067</t>
+          <t>256746</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>319516</t>
+          <t>323336</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3187041</t>
+          <t>3187904</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3220393</t>
+          <t>3220615</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3131502</t>
+          <t>3131388</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3188201</t>
+          <t>3188530</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6335206</t>
+          <t>6331386</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6395655</t>
+          <t>6397976</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,14%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10729</t>
+          <t>10902</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29094</t>
+          <t>27478</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>53560</t>
+          <t>52582</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>84617</t>
+          <t>82948</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>70995</t>
+          <t>68606</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>107857</t>
+          <t>104661</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,5%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>671670</t>
+          <t>673286</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>690035</t>
+          <t>689862</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>610456</t>
+          <t>612125</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>641513</t>
+          <t>642491</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1287980</t>
+          <t>1291176</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1324842</t>
+          <t>1327231</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>95,08%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24320</t>
+          <t>25258</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50697</t>
+          <t>51002</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>67217</t>
+          <t>67289</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>102157</t>
+          <t>103275</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>99013</t>
+          <t>99342</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>142863</t>
+          <t>143952</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,04%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>967250</t>
+          <t>966945</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>993627</t>
+          <t>992689</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>924538</t>
+          <t>923420</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>959478</t>
+          <t>959406</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1901779</t>
+          <t>1900690</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1945629</t>
+          <t>1945300</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,14%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8247</t>
+          <t>8158</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28074</t>
+          <t>27275</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40979</t>
+          <t>42228</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72308</t>
+          <t>71730</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55592</t>
+          <t>57548</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>91426</t>
+          <t>90125</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>727423</t>
+          <t>728222</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>747250</t>
+          <t>747339</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>703975</t>
+          <t>704553</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>735304</t>
+          <t>734055</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1440354</t>
+          <t>1441655</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1476188</t>
+          <t>1474232</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,24%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24926</t>
+          <t>25943</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52906</t>
+          <t>52559</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>72192</t>
+          <t>72822</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>108782</t>
+          <t>110045</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>104745</t>
+          <t>106384</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>150736</t>
+          <t>154836</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>891033</t>
+          <t>891380</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>919013</t>
+          <t>917996</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>939981</t>
+          <t>938718</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>976571</t>
+          <t>975941</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1841967</t>
+          <t>1837867</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1887958</t>
+          <t>1886319</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,66%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>86537</t>
+          <t>86262</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>132995</t>
+          <t>133819</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>264554</t>
+          <t>262954</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>331394</t>
+          <t>334706</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>364473</t>
+          <t>362663</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>448511</t>
+          <t>444459</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3285152</t>
+          <t>3284328</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3331610</t>
+          <t>3331885</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3215421</t>
+          <t>3212109</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3282261</t>
+          <t>3283861</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6516450</t>
+          <t>6520502</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6600488</t>
+          <t>6602298</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,79%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6879</t>
+          <t>6986</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21308</t>
+          <t>21828</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>45034</t>
+          <t>43948</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>73523</t>
+          <t>73177</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55104</t>
+          <t>54041</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86750</t>
+          <t>87378</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>653492</t>
+          <t>652972</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>667921</t>
+          <t>667814</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>599316</t>
+          <t>599662</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>627805</t>
+          <t>628891</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1260889</t>
+          <t>1260261</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1292535</t>
+          <t>1293598</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,99%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10464</t>
+          <t>10121</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26873</t>
+          <t>26675</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60712</t>
+          <t>60538</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>94435</t>
+          <t>94950</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>76703</t>
+          <t>75331</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>114567</t>
+          <t>115332</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>995558</t>
+          <t>995756</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1011967</t>
+          <t>1012310</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>948478</t>
+          <t>947963</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>982201</t>
+          <t>982375</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1950777</t>
+          <t>1950012</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1988641</t>
+          <t>1990013</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,35%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8834</t>
+          <t>9311</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25533</t>
+          <t>26108</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31150</t>
+          <t>31280</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58152</t>
+          <t>57977</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43784</t>
+          <t>43616</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>76220</t>
+          <t>75603</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>734019</t>
+          <t>733444</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>750718</t>
+          <t>750241</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>726859</t>
+          <t>727034</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>753861</t>
+          <t>753731</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1468343</t>
+          <t>1468960</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1500779</t>
+          <t>1500947</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,18%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19398</t>
+          <t>19779</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40854</t>
+          <t>42101</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59250</t>
+          <t>60426</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>95609</t>
+          <t>95325</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>85580</t>
+          <t>85189</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>124274</t>
+          <t>126736</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>896713</t>
+          <t>895466</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>918169</t>
+          <t>917788</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>948170</t>
+          <t>948454</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>984529</t>
+          <t>983353</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1857072</t>
+          <t>1854610</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1895766</t>
+          <t>1896157</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,7%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>58629</t>
+          <t>58476</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>92928</t>
+          <t>94031</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>220920</t>
+          <t>223117</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>288598</t>
+          <t>286399</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>294186</t>
+          <t>294586</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>365908</t>
+          <t>366535</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3301422</t>
+          <t>3300319</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3335721</t>
+          <t>3335874</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3255944</t>
+          <t>3258143</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3323622</t>
+          <t>3321425</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6572984</t>
+          <t>6572357</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6644706</t>
+          <t>6644306</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,75%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>30619</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22055</t>
+          <t>23787</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43288</t>
+          <t>47414</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>45355</t>
+          <t>48849</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36975</t>
+          <t>39681</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56402</t>
+          <t>59785</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>75974</t>
+          <t>82426</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>62327</t>
+          <t>66884</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>90678</t>
+          <t>99816</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>604332</t>
+          <t>656638</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>591663</t>
+          <t>642801</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>612896</t>
+          <t>666428</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>630067</t>
+          <t>683933</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>619020</t>
+          <t>672997</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>638447</t>
+          <t>693101</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1234399</t>
+          <t>1340571</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1219695</t>
+          <t>1323181</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1248046</t>
+          <t>1356113</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,3%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>634951</t>
+          <t>690215</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>634951</t>
+          <t>690215</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>634951</t>
+          <t>690215</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675422</t>
+          <t>732782</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675422</t>
+          <t>732782</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675422</t>
+          <t>732782</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1310373</t>
+          <t>1422997</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1310373</t>
+          <t>1422997</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1310373</t>
+          <t>1422997</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24622</t>
+          <t>26756</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12015</t>
+          <t>17548</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37703</t>
+          <t>37943</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>62666</t>
+          <t>69020</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52380</t>
+          <t>56216</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>76182</t>
+          <t>83122</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>87287</t>
+          <t>95776</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>57894</t>
+          <t>80596</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>106141</t>
+          <t>114883</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1168242</t>
+          <t>1022161</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1155161</t>
+          <t>1010974</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1180849</t>
+          <t>1031369</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>895440</t>
+          <t>1001818</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>881924</t>
+          <t>987716</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>905726</t>
+          <t>1014622</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2063684</t>
+          <t>2023979</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2044830</t>
+          <t>2004872</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2093077</t>
+          <t>2039159</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>96,2%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>23382</t>
+          <t>26739</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15521</t>
+          <t>18611</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35068</t>
+          <t>39171</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>61237</t>
+          <t>67242</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31075</t>
+          <t>55988</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>85083</t>
+          <t>83116</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>84619</t>
+          <t>93980</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54283</t>
+          <t>79072</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>105554</t>
+          <t>113495</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>680302</t>
+          <t>775347</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>668616</t>
+          <t>762915</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>688163</t>
+          <t>783475</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>871563</t>
+          <t>744421</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>847717</t>
+          <t>728547</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>901725</t>
+          <t>755675</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1551865</t>
+          <t>1519768</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1530930</t>
+          <t>1500253</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1582201</t>
+          <t>1534676</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>95,1%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>932800</t>
+          <t>811663</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>932800</t>
+          <t>811663</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>932800</t>
+          <t>811663</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1636484</t>
+          <t>1613748</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1636484</t>
+          <t>1613748</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1636484</t>
+          <t>1613748</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>33134</t>
+          <t>34683</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24047</t>
+          <t>24875</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44002</t>
+          <t>45674</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>92939</t>
+          <t>101146</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>72509</t>
+          <t>87063</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>109459</t>
+          <t>117046</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>126073</t>
+          <t>135828</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>106090</t>
+          <t>116711</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>147207</t>
+          <t>156038</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>893697</t>
+          <t>955379</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>882829</t>
+          <t>944388</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>902784</t>
+          <t>965187</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>998435</t>
+          <t>1015885</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>981915</t>
+          <t>999985</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1018865</t>
+          <t>1029968</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1892132</t>
+          <t>1971265</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1870998</t>
+          <t>1951055</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1912115</t>
+          <t>1990382</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,46%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>111757</t>
+          <t>121754</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>85505</t>
+          <t>100742</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>134337</t>
+          <t>146123</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>262196</t>
+          <t>286257</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>214142</t>
+          <t>259442</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>293572</t>
+          <t>312595</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>373953</t>
+          <t>408011</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>323773</t>
+          <t>375286</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>413007</t>
+          <t>444858</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3346573</t>
+          <t>3409526</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3323993</t>
+          <t>3385157</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3372825</t>
+          <t>3430538</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3395506</t>
+          <t>3446056</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3364130</t>
+          <t>3419718</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3443560</t>
+          <t>3472871</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6742079</t>
+          <t>6855582</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6703025</t>
+          <t>6818735</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6792259</t>
+          <t>6888307</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>94,83%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3657702</t>
+          <t>3732313</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3657702</t>
+          <t>3732313</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3657702</t>
+          <t>3732313</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7116032</t>
+          <t>7263593</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7116032</t>
+          <t>7263593</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7116032</t>
+          <t>7263593</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
